--- a/data/trans_dic/IP12B$alergia-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,21</t>
+          <t>0,0; 54,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,54</t>
+          <t>0,0; 50,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,81</t>
+          <t>0,0; 30,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,37</t>
+          <t>0,0; 55,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,96</t>
+          <t>0,0; 29,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,09</t>
+          <t>0,0; 26,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,81</t>
+          <t>0,0; 33,92</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,07</t>
+          <t>0,0; 39,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,99</t>
+          <t>0,0; 20,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,88</t>
+          <t>0,0; 59,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,18</t>
+          <t>0,0; 35,65</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,97</t>
+          <t>0,0; 26,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,61</t>
+          <t>0,0; 20,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,37</t>
+          <t>0,0; 23,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,5</t>
+          <t>0,0; 23,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 19,23</t>
+          <t>2,24; 18,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 16,09</t>
+          <t>1,8; 15,61</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,32</t>
+          <t>0,0; 40,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,74</t>
+          <t>0,0; 32,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,35</t>
+          <t>0,0; 42,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,9</t>
+          <t>0,0; 32,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,37</t>
+          <t>0,0; 24,13</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,41</t>
+          <t>0,0; 67,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,24</t>
+          <t>0,0; 54,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,2</t>
+          <t>0,0; 70,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,7</t>
+          <t>0,0; 40,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,07</t>
+          <t>0,0; 47,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,58</t>
+          <t>0,0; 37,11</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,64</t>
+          <t>1,51; 13,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 8,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 15,51</t>
+          <t>2,5; 14,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,06</t>
+          <t>1,27; 10,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,73</t>
+          <t>1,7; 14,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 14,43</t>
+          <t>1,41; 13,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,26</t>
+          <t>1,69; 9,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,54</t>
+          <t>1,51; 8,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,33</t>
+          <t>3,23; 11,61</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4818</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2651</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3660</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4190</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4018</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4610</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2612</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2640</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2980</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3409</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4680</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4242</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5301</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3945</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>894; 7292</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>673; 5844</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3309</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3375</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2576</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4679</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4272</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2571</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3518</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2754</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2632</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4377</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2706</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5129</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>6230</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>628; 5639</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5295</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1322; 7652</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>592; 5107</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>996; 8458</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>646; 6062</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1493; 8091</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1800; 10711</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3187; 11467</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$alergia-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,42</t>
+          <t>0,0; 48,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,13</t>
+          <t>0,0; 48,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,63</t>
+          <t>0,0; 30,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,35</t>
+          <t>0,0; 55,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,08</t>
+          <t>0,0; 29,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,35</t>
+          <t>0,0; 36,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,92</t>
+          <t>0,0; 40,86</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,95</t>
+          <t>0,0; 39,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,96</t>
+          <t>0,0; 28,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,23</t>
+          <t>0,0; 57,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,65</t>
+          <t>0,0; 34,5</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,96</t>
+          <t>0,0; 28,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,64</t>
+          <t>0,0; 21,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,46</t>
+          <t>0,0; 21,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,37</t>
+          <t>0,0; 27,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 18,25</t>
+          <t>1,81; 19,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 15,61</t>
+          <t>1,73; 16,19</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,23</t>
+          <t>0,0; 41,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,85</t>
+          <t>0,0; 33,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,85</t>
+          <t>0,0; 42,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,86</t>
+          <t>0,0; 31,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,13</t>
+          <t>0,0; 21,85</t>
         </is>
       </c>
     </row>
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,47</t>
+          <t>0,0; 67,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,97</t>
+          <t>0,0; 54,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,87</t>
+          <t>0,0; 67,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,01</t>
+          <t>0,0; 40,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,05</t>
+          <t>0,0; 46,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,11</t>
+          <t>0,0; 36,92</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,6</t>
+          <t>1,52; 13,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,73</t>
+          <t>0,0; 9,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 14,49</t>
+          <t>2,47; 15,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,93</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,42</t>
+          <t>1,54; 14,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 13,19</t>
+          <t>1,47; 13,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,18</t>
+          <t>1,61; 9,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,98</t>
+          <t>1,49; 8,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,61</t>
+          <t>3,14; 12,5</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3130</t>
+          <t>0; 2767</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4818</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2651</t>
+          <t>0; 2637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3660</t>
+          <t>0; 3682</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4190</t>
+          <t>0; 4200</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4018</t>
+          <t>0; 5590</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4610</t>
+          <t>0; 5553</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2612</t>
+          <t>0; 2599</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2640</t>
+          <t>0; 3608</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2980</t>
+          <t>0; 2911</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3409</t>
+          <t>0; 3299</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4680</t>
+          <t>0; 4993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4242</t>
+          <t>0; 4392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 4889</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>894; 7292</t>
+          <t>725; 7871</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>673; 5844</t>
+          <t>649; 6061</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3309</t>
+          <t>0; 3442</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3375</t>
+          <t>0; 3455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2576</t>
+          <t>0; 2545</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4679</t>
+          <t>0; 4518</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4272</t>
+          <t>0; 3869</t>
         </is>
       </c>
     </row>
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2571</t>
+          <t>0; 2570</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3518</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2754</t>
+          <t>0; 2620</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2632</t>
+          <t>0; 2633</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4377</t>
+          <t>0; 4296</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2706</t>
+          <t>0; 2692</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>628; 5639</t>
+          <t>629; 5650</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5295</t>
+          <t>0; 5563</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1322; 7652</t>
+          <t>1306; 8130</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>592; 5107</t>
+          <t>0; 4541</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>996; 8458</t>
+          <t>905; 8252</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>646; 6062</t>
+          <t>675; 6031</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1493; 8091</t>
+          <t>1420; 8521</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1800; 10711</t>
+          <t>1774; 10371</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3187; 11467</t>
+          <t>3096; 12338</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$alergia-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,11%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16,07%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,1</t>
+          <t>0,0; 30,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,47</t>
+          <t>0,0; 47,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 47,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,16</t>
+          <t>0,0; 28,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,66</t>
+          <t>0,0; 32,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,86</t>
+          <t>0,0; 33,81</t>
         </is>
       </c>
     </row>
@@ -735,22 +735,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,67%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 49,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,64</t>
+          <t>0,0; 27,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>13,05%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 57,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,5</t>
+          <t>0,0; 29,18</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,04%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,2%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,76</t>
+          <t>0,0; 26,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 23,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,63</t>
+          <t>0,0; 26,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,85</t>
+          <t>0,0; 18,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 19,7</t>
+          <t>2,17; 19,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 16,19</t>
+          <t>1,68; 16,09</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>9,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,78%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,85</t>
+          <t>0,0; 46,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,34</t>
+          <t>0,0; 46,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,73</t>
+          <t>0,0; 27,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,85</t>
+          <t>0,0; 23,37</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 67,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 67,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,02</t>
+          <t>0,0; 48,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,18</t>
+          <t>0,0; 47,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,92</t>
+          <t>0,0; 37,58</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,11%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6,85%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,62</t>
+          <t>1,25; 12,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,17</t>
+          <t>1,58; 14,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 15,4</t>
+          <t>1,44; 14,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>1,51; 13,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 14,07</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,13</t>
+          <t>2,59; 15,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,66</t>
+          <t>1,69; 9,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,69</t>
+          <t>1,64; 9,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 12,5</t>
+          <t>3,06; 11,33</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1538,27 +1538,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>696</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1545</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2767</t>
+          <t>0; 2666</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3662</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4701</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2637</t>
+          <t>0; 2716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3682</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4570</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4200</t>
+          <t>0; 4172</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5590</t>
+          <t>0; 4894</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5553</t>
+          <t>0; 4595</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1696,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2599</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3209</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3608</t>
+          <t>0; 3526</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3299</t>
+          <t>0; 2791</t>
         </is>
       </c>
     </row>
@@ -2080,27 +2080,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1570</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1274</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4993</t>
+          <t>0; 5959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4392</t>
+          <t>0; 3966</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4889</t>
+          <t>0; 4682</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4701</t>
+          <t>0; 3825</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>725; 7871</t>
+          <t>869; 7686</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>649; 6061</t>
+          <t>627; 6021</t>
         </is>
       </c>
     </row>
@@ -2195,22 +2195,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>799</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3442</t>
+          <t>0; 2786</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3455</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2545</t>
+          <t>0; 3810</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3363</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4518</t>
+          <t>0; 3973</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3869</t>
+          <t>0; 4138</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>984</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2568</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3535</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2611</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2570</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2620</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2633</t>
+          <t>0; 3204</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4296</t>
+          <t>0; 4379</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2692</t>
+          <t>0; 2740</t>
         </is>
       </c>
     </row>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2120</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1570</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3618</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3559</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>629; 5650</t>
+          <t>586; 5633</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5563</t>
+          <t>927; 8637</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1306; 8130</t>
+          <t>660; 6631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4541</t>
+          <t>627; 5658</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>905; 8252</t>
+          <t>0; 4659</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>675; 6031</t>
+          <t>1366; 8189</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1420; 8521</t>
+          <t>1494; 8164</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1774; 10371</t>
+          <t>1952; 11386</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3096; 12338</t>
+          <t>3020; 11191</t>
         </is>
       </c>
     </row>
